--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9200,6 +9200,1631 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122805707</v>
+      </c>
+      <c r="B70" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>505815</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6527608</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122805721</v>
+      </c>
+      <c r="B71" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>505794</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6527502</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122805709</v>
+      </c>
+      <c r="B72" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>505799</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6527616</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122805706</v>
+      </c>
+      <c r="B73" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>505819</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6527642</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122805717</v>
+      </c>
+      <c r="B74" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>505815</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6527554</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122805711</v>
+      </c>
+      <c r="B75" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>505805</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6527609</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122805718</v>
+      </c>
+      <c r="B76" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>505822</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6527537</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122805715</v>
+      </c>
+      <c r="B77" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>505807</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6527517</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122805720</v>
+      </c>
+      <c r="B78" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>505791</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6527512</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122805713</v>
+      </c>
+      <c r="B79" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>505824</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6527597</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122805719</v>
+      </c>
+      <c r="B80" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>505805</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6527537</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122805716</v>
+      </c>
+      <c r="B81" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>505804</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6527537</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122805708</v>
+      </c>
+      <c r="B82" t="n">
+        <v>83374</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>505802</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6527622</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805707</v>
+        <v>122805709</v>
       </c>
       <c r="B70" t="n">
         <v>83374</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505815</v>
+        <v>505799</v>
       </c>
       <c r="R70" t="n">
-        <v>6527608</v>
+        <v>6527616</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805721</v>
+        <v>122805707</v>
       </c>
       <c r="B71" t="n">
         <v>83374</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505794</v>
+        <v>505815</v>
       </c>
       <c r="R71" t="n">
-        <v>6527502</v>
+        <v>6527608</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805709</v>
+        <v>122805719</v>
       </c>
       <c r="B72" t="n">
         <v>83374</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505799</v>
+        <v>505805</v>
       </c>
       <c r="R72" t="n">
-        <v>6527616</v>
+        <v>6527537</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805706</v>
+        <v>122805715</v>
       </c>
       <c r="B73" t="n">
         <v>83374</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505819</v>
+        <v>505807</v>
       </c>
       <c r="R73" t="n">
-        <v>6527642</v>
+        <v>6527517</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805717</v>
+        <v>122805708</v>
       </c>
       <c r="B74" t="n">
         <v>83374</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505815</v>
+        <v>505802</v>
       </c>
       <c r="R74" t="n">
-        <v>6527554</v>
+        <v>6527622</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805711</v>
+        <v>122805718</v>
       </c>
       <c r="B75" t="n">
         <v>83374</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505805</v>
+        <v>505822</v>
       </c>
       <c r="R75" t="n">
-        <v>6527609</v>
+        <v>6527537</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805718</v>
+        <v>122805711</v>
       </c>
       <c r="B76" t="n">
         <v>83374</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505822</v>
+        <v>505805</v>
       </c>
       <c r="R76" t="n">
-        <v>6527537</v>
+        <v>6527609</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805715</v>
+        <v>122805713</v>
       </c>
       <c r="B77" t="n">
         <v>83374</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505807</v>
+        <v>505824</v>
       </c>
       <c r="R77" t="n">
-        <v>6527517</v>
+        <v>6527597</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805713</v>
+        <v>122805717</v>
       </c>
       <c r="B79" t="n">
         <v>83374</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505824</v>
+        <v>505815</v>
       </c>
       <c r="R79" t="n">
-        <v>6527597</v>
+        <v>6527554</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805719</v>
+        <v>122805721</v>
       </c>
       <c r="B80" t="n">
         <v>83374</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505805</v>
+        <v>505794</v>
       </c>
       <c r="R80" t="n">
-        <v>6527537</v>
+        <v>6527502</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805708</v>
+        <v>122805706</v>
       </c>
       <c r="B82" t="n">
         <v>83374</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505802</v>
+        <v>505819</v>
       </c>
       <c r="R82" t="n">
-        <v>6527622</v>
+        <v>6527642</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805713</v>
+        <v>122805720</v>
       </c>
       <c r="B77" t="n">
         <v>83374</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505824</v>
+        <v>505791</v>
       </c>
       <c r="R77" t="n">
-        <v>6527597</v>
+        <v>6527512</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805720</v>
+        <v>122805713</v>
       </c>
       <c r="B78" t="n">
         <v>83374</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505791</v>
+        <v>505824</v>
       </c>
       <c r="R78" t="n">
-        <v>6527512</v>
+        <v>6527597</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805709</v>
+        <v>122805716</v>
       </c>
       <c r="B70" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505799</v>
+        <v>505804</v>
       </c>
       <c r="R70" t="n">
-        <v>6527616</v>
+        <v>6527537</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805707</v>
+        <v>122805711</v>
       </c>
       <c r="B71" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505815</v>
+        <v>505805</v>
       </c>
       <c r="R71" t="n">
-        <v>6527608</v>
+        <v>6527609</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805719</v>
+        <v>122805708</v>
       </c>
       <c r="B72" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505805</v>
+        <v>505802</v>
       </c>
       <c r="R72" t="n">
-        <v>6527537</v>
+        <v>6527622</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9580,7 +9580,7 @@
         <v>122805715</v>
       </c>
       <c r="B73" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805708</v>
+        <v>122805717</v>
       </c>
       <c r="B74" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505802</v>
+        <v>505815</v>
       </c>
       <c r="R74" t="n">
-        <v>6527622</v>
+        <v>6527554</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,10 +9827,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805718</v>
+        <v>122805707</v>
       </c>
       <c r="B75" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505822</v>
+        <v>505815</v>
       </c>
       <c r="R75" t="n">
-        <v>6527537</v>
+        <v>6527608</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805711</v>
+        <v>122805718</v>
       </c>
       <c r="B76" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505805</v>
+        <v>505822</v>
       </c>
       <c r="R76" t="n">
-        <v>6527609</v>
+        <v>6527537</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,10 +10077,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805720</v>
+        <v>122805721</v>
       </c>
       <c r="B77" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505791</v>
+        <v>505794</v>
       </c>
       <c r="R77" t="n">
-        <v>6527512</v>
+        <v>6527502</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,10 +10202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805713</v>
+        <v>122805720</v>
       </c>
       <c r="B78" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505824</v>
+        <v>505791</v>
       </c>
       <c r="R78" t="n">
-        <v>6527597</v>
+        <v>6527512</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805717</v>
+        <v>122805713</v>
       </c>
       <c r="B79" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505815</v>
+        <v>505824</v>
       </c>
       <c r="R79" t="n">
-        <v>6527554</v>
+        <v>6527597</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805721</v>
+        <v>122805709</v>
       </c>
       <c r="B80" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505794</v>
+        <v>505799</v>
       </c>
       <c r="R80" t="n">
-        <v>6527502</v>
+        <v>6527616</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805716</v>
+        <v>122805706</v>
       </c>
       <c r="B81" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505804</v>
+        <v>505819</v>
       </c>
       <c r="R81" t="n">
-        <v>6527537</v>
+        <v>6527642</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805706</v>
+        <v>122805719</v>
       </c>
       <c r="B82" t="n">
-        <v>83374</v>
+        <v>83378</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505819</v>
+        <v>505805</v>
       </c>
       <c r="R82" t="n">
-        <v>6527642</v>
+        <v>6527537</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805716</v>
+        <v>122805707</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505804</v>
+        <v>505815</v>
       </c>
       <c r="R70" t="n">
-        <v>6527537</v>
+        <v>6527608</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805711</v>
+        <v>122805721</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505805</v>
+        <v>505794</v>
       </c>
       <c r="R71" t="n">
-        <v>6527609</v>
+        <v>6527502</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805708</v>
+        <v>122805706</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505802</v>
+        <v>505819</v>
       </c>
       <c r="R72" t="n">
-        <v>6527622</v>
+        <v>6527642</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805715</v>
+        <v>122805711</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505807</v>
+        <v>505805</v>
       </c>
       <c r="R73" t="n">
-        <v>6527517</v>
+        <v>6527609</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805717</v>
+        <v>122805713</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505815</v>
+        <v>505824</v>
       </c>
       <c r="R74" t="n">
-        <v>6527554</v>
+        <v>6527597</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805707</v>
+        <v>122805708</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505815</v>
+        <v>505802</v>
       </c>
       <c r="R75" t="n">
-        <v>6527608</v>
+        <v>6527622</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805721</v>
+        <v>122805716</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505794</v>
+        <v>505804</v>
       </c>
       <c r="R77" t="n">
-        <v>6527502</v>
+        <v>6527537</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805720</v>
+        <v>122805719</v>
       </c>
       <c r="B78" t="n">
         <v>83378</v>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505791</v>
+        <v>505805</v>
       </c>
       <c r="R78" t="n">
-        <v>6527512</v>
+        <v>6527537</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805713</v>
+        <v>122805715</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505824</v>
+        <v>505807</v>
       </c>
       <c r="R79" t="n">
-        <v>6527597</v>
+        <v>6527517</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805709</v>
+        <v>122805720</v>
       </c>
       <c r="B80" t="n">
         <v>83378</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505799</v>
+        <v>505791</v>
       </c>
       <c r="R80" t="n">
-        <v>6527616</v>
+        <v>6527512</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805706</v>
+        <v>122805717</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505819</v>
+        <v>505815</v>
       </c>
       <c r="R81" t="n">
-        <v>6527642</v>
+        <v>6527554</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805719</v>
+        <v>122805709</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505805</v>
+        <v>505799</v>
       </c>
       <c r="R82" t="n">
-        <v>6527537</v>
+        <v>6527616</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805707</v>
+        <v>122805721</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505815</v>
+        <v>505794</v>
       </c>
       <c r="R70" t="n">
-        <v>6527608</v>
+        <v>6527502</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805721</v>
+        <v>122805717</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505794</v>
+        <v>505815</v>
       </c>
       <c r="R71" t="n">
-        <v>6527502</v>
+        <v>6527554</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805706</v>
+        <v>122805719</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505819</v>
+        <v>505805</v>
       </c>
       <c r="R72" t="n">
-        <v>6527642</v>
+        <v>6527537</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805711</v>
+        <v>122805708</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505805</v>
+        <v>505802</v>
       </c>
       <c r="R73" t="n">
-        <v>6527609</v>
+        <v>6527622</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805713</v>
+        <v>122805715</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505824</v>
+        <v>505807</v>
       </c>
       <c r="R74" t="n">
-        <v>6527597</v>
+        <v>6527517</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805708</v>
+        <v>122805706</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505802</v>
+        <v>505819</v>
       </c>
       <c r="R75" t="n">
-        <v>6527622</v>
+        <v>6527642</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805718</v>
+        <v>122805709</v>
       </c>
       <c r="B76" t="n">
         <v>83378</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505822</v>
+        <v>505799</v>
       </c>
       <c r="R76" t="n">
-        <v>6527537</v>
+        <v>6527616</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805716</v>
+        <v>122805707</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505804</v>
+        <v>505815</v>
       </c>
       <c r="R77" t="n">
-        <v>6527537</v>
+        <v>6527608</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805719</v>
+        <v>122805716</v>
       </c>
       <c r="B78" t="n">
         <v>83378</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505805</v>
+        <v>505804</v>
       </c>
       <c r="R78" t="n">
         <v>6527537</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805715</v>
+        <v>122805713</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505807</v>
+        <v>505824</v>
       </c>
       <c r="R79" t="n">
-        <v>6527517</v>
+        <v>6527597</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805720</v>
+        <v>122805718</v>
       </c>
       <c r="B80" t="n">
         <v>83378</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505791</v>
+        <v>505822</v>
       </c>
       <c r="R80" t="n">
-        <v>6527512</v>
+        <v>6527537</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805717</v>
+        <v>122805720</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505815</v>
+        <v>505791</v>
       </c>
       <c r="R81" t="n">
-        <v>6527554</v>
+        <v>6527512</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805709</v>
+        <v>122805711</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505799</v>
+        <v>505805</v>
       </c>
       <c r="R82" t="n">
-        <v>6527616</v>
+        <v>6527609</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805721</v>
+        <v>122805719</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505794</v>
+        <v>505805</v>
       </c>
       <c r="R70" t="n">
-        <v>6527502</v>
+        <v>6527537</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805717</v>
+        <v>122805715</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505815</v>
+        <v>505807</v>
       </c>
       <c r="R71" t="n">
-        <v>6527554</v>
+        <v>6527517</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805719</v>
+        <v>122805709</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505805</v>
+        <v>505799</v>
       </c>
       <c r="R72" t="n">
-        <v>6527537</v>
+        <v>6527616</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805708</v>
+        <v>122805717</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505802</v>
+        <v>505815</v>
       </c>
       <c r="R73" t="n">
-        <v>6527622</v>
+        <v>6527554</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805715</v>
+        <v>122805718</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505807</v>
+        <v>505822</v>
       </c>
       <c r="R74" t="n">
-        <v>6527517</v>
+        <v>6527537</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805706</v>
+        <v>122805721</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505819</v>
+        <v>505794</v>
       </c>
       <c r="R75" t="n">
-        <v>6527642</v>
+        <v>6527502</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805709</v>
+        <v>122805706</v>
       </c>
       <c r="B76" t="n">
         <v>83378</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505799</v>
+        <v>505819</v>
       </c>
       <c r="R76" t="n">
-        <v>6527616</v>
+        <v>6527642</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805707</v>
+        <v>122805720</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505815</v>
+        <v>505791</v>
       </c>
       <c r="R77" t="n">
-        <v>6527608</v>
+        <v>6527512</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805713</v>
+        <v>122805711</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505824</v>
+        <v>505805</v>
       </c>
       <c r="R79" t="n">
-        <v>6527597</v>
+        <v>6527609</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805718</v>
+        <v>122805707</v>
       </c>
       <c r="B80" t="n">
         <v>83378</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505822</v>
+        <v>505815</v>
       </c>
       <c r="R80" t="n">
-        <v>6527537</v>
+        <v>6527608</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805720</v>
+        <v>122805713</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505791</v>
+        <v>505824</v>
       </c>
       <c r="R81" t="n">
-        <v>6527512</v>
+        <v>6527597</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805711</v>
+        <v>122805708</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505805</v>
+        <v>505802</v>
       </c>
       <c r="R82" t="n">
-        <v>6527609</v>
+        <v>6527622</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805715</v>
+        <v>122805709</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505807</v>
+        <v>505799</v>
       </c>
       <c r="R71" t="n">
-        <v>6527517</v>
+        <v>6527616</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805709</v>
+        <v>122805715</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505799</v>
+        <v>505807</v>
       </c>
       <c r="R72" t="n">
-        <v>6527616</v>
+        <v>6527517</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805709</v>
+        <v>122805715</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505799</v>
+        <v>505807</v>
       </c>
       <c r="R71" t="n">
-        <v>6527616</v>
+        <v>6527517</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805715</v>
+        <v>122805709</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505807</v>
+        <v>505799</v>
       </c>
       <c r="R72" t="n">
-        <v>6527517</v>
+        <v>6527616</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805719</v>
+        <v>122805706</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505805</v>
+        <v>505819</v>
       </c>
       <c r="R70" t="n">
-        <v>6527537</v>
+        <v>6527642</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805715</v>
+        <v>122805717</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505807</v>
+        <v>505815</v>
       </c>
       <c r="R71" t="n">
-        <v>6527517</v>
+        <v>6527554</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805709</v>
+        <v>122805708</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505799</v>
+        <v>505802</v>
       </c>
       <c r="R72" t="n">
-        <v>6527616</v>
+        <v>6527622</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805717</v>
+        <v>122805719</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505815</v>
+        <v>505805</v>
       </c>
       <c r="R73" t="n">
-        <v>6527554</v>
+        <v>6527537</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805718</v>
+        <v>122805721</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505822</v>
+        <v>505794</v>
       </c>
       <c r="R74" t="n">
-        <v>6527537</v>
+        <v>6527502</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805721</v>
+        <v>122805718</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505794</v>
+        <v>505822</v>
       </c>
       <c r="R75" t="n">
-        <v>6527502</v>
+        <v>6527537</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805706</v>
+        <v>122805720</v>
       </c>
       <c r="B76" t="n">
         <v>83378</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505819</v>
+        <v>505791</v>
       </c>
       <c r="R76" t="n">
-        <v>6527642</v>
+        <v>6527512</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805720</v>
+        <v>122805713</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505791</v>
+        <v>505824</v>
       </c>
       <c r="R77" t="n">
-        <v>6527512</v>
+        <v>6527597</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805716</v>
+        <v>122805711</v>
       </c>
       <c r="B78" t="n">
         <v>83378</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505804</v>
+        <v>505805</v>
       </c>
       <c r="R78" t="n">
-        <v>6527537</v>
+        <v>6527609</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805711</v>
+        <v>122805716</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505805</v>
+        <v>505804</v>
       </c>
       <c r="R79" t="n">
-        <v>6527609</v>
+        <v>6527537</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805707</v>
+        <v>122805709</v>
       </c>
       <c r="B80" t="n">
         <v>83378</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505815</v>
+        <v>505799</v>
       </c>
       <c r="R80" t="n">
-        <v>6527608</v>
+        <v>6527616</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805713</v>
+        <v>122805715</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505824</v>
+        <v>505807</v>
       </c>
       <c r="R81" t="n">
-        <v>6527597</v>
+        <v>6527517</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805708</v>
+        <v>122805707</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505802</v>
+        <v>505815</v>
       </c>
       <c r="R82" t="n">
-        <v>6527622</v>
+        <v>6527608</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805706</v>
+        <v>122805716</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505819</v>
+        <v>505804</v>
       </c>
       <c r="R70" t="n">
-        <v>6527642</v>
+        <v>6527537</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805717</v>
+        <v>122805708</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505815</v>
+        <v>505802</v>
       </c>
       <c r="R71" t="n">
-        <v>6527554</v>
+        <v>6527622</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805708</v>
+        <v>122805707</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505802</v>
+        <v>505815</v>
       </c>
       <c r="R72" t="n">
-        <v>6527622</v>
+        <v>6527608</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805719</v>
+        <v>122805715</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505805</v>
+        <v>505807</v>
       </c>
       <c r="R73" t="n">
-        <v>6527537</v>
+        <v>6527517</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805721</v>
+        <v>122805720</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505794</v>
+        <v>505791</v>
       </c>
       <c r="R74" t="n">
-        <v>6527502</v>
+        <v>6527512</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805720</v>
+        <v>122805711</v>
       </c>
       <c r="B76" t="n">
         <v>83378</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505791</v>
+        <v>505805</v>
       </c>
       <c r="R76" t="n">
-        <v>6527512</v>
+        <v>6527609</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805713</v>
+        <v>122805719</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505824</v>
+        <v>505805</v>
       </c>
       <c r="R77" t="n">
-        <v>6527597</v>
+        <v>6527537</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805711</v>
+        <v>122805717</v>
       </c>
       <c r="B78" t="n">
         <v>83378</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505805</v>
+        <v>505815</v>
       </c>
       <c r="R78" t="n">
-        <v>6527609</v>
+        <v>6527554</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805716</v>
+        <v>122805706</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505804</v>
+        <v>505819</v>
       </c>
       <c r="R79" t="n">
-        <v>6527537</v>
+        <v>6527642</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805709</v>
+        <v>122805721</v>
       </c>
       <c r="B80" t="n">
         <v>83378</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505799</v>
+        <v>505794</v>
       </c>
       <c r="R80" t="n">
-        <v>6527616</v>
+        <v>6527502</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805715</v>
+        <v>122805713</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505807</v>
+        <v>505824</v>
       </c>
       <c r="R81" t="n">
-        <v>6527517</v>
+        <v>6527597</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805707</v>
+        <v>122805709</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505815</v>
+        <v>505799</v>
       </c>
       <c r="R82" t="n">
-        <v>6527608</v>
+        <v>6527616</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805720</v>
+        <v>122805718</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505791</v>
+        <v>505822</v>
       </c>
       <c r="R74" t="n">
-        <v>6527512</v>
+        <v>6527537</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805718</v>
+        <v>122805720</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505822</v>
+        <v>505791</v>
       </c>
       <c r="R75" t="n">
-        <v>6527537</v>
+        <v>6527512</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805716</v>
+        <v>122805715</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505804</v>
+        <v>505807</v>
       </c>
       <c r="R70" t="n">
-        <v>6527537</v>
+        <v>6527517</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805708</v>
+        <v>122805707</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505802</v>
+        <v>505815</v>
       </c>
       <c r="R71" t="n">
-        <v>6527622</v>
+        <v>6527608</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805707</v>
+        <v>122805720</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505815</v>
+        <v>505791</v>
       </c>
       <c r="R72" t="n">
-        <v>6527608</v>
+        <v>6527512</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805715</v>
+        <v>122805708</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505807</v>
+        <v>505802</v>
       </c>
       <c r="R73" t="n">
-        <v>6527517</v>
+        <v>6527622</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805718</v>
+        <v>122805719</v>
       </c>
       <c r="B74" t="n">
         <v>83378</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505822</v>
+        <v>505805</v>
       </c>
       <c r="R74" t="n">
         <v>6527537</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805720</v>
+        <v>122805709</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505791</v>
+        <v>505799</v>
       </c>
       <c r="R75" t="n">
-        <v>6527512</v>
+        <v>6527616</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805711</v>
+        <v>122805706</v>
       </c>
       <c r="B76" t="n">
         <v>83378</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505805</v>
+        <v>505819</v>
       </c>
       <c r="R76" t="n">
-        <v>6527609</v>
+        <v>6527642</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805719</v>
+        <v>122805713</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505805</v>
+        <v>505824</v>
       </c>
       <c r="R77" t="n">
-        <v>6527537</v>
+        <v>6527597</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805717</v>
+        <v>122805718</v>
       </c>
       <c r="B78" t="n">
         <v>83378</v>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505815</v>
+        <v>505822</v>
       </c>
       <c r="R78" t="n">
-        <v>6527554</v>
+        <v>6527537</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805706</v>
+        <v>122805721</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505819</v>
+        <v>505794</v>
       </c>
       <c r="R79" t="n">
-        <v>6527642</v>
+        <v>6527502</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805721</v>
+        <v>122805711</v>
       </c>
       <c r="B80" t="n">
         <v>83378</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505794</v>
+        <v>505805</v>
       </c>
       <c r="R80" t="n">
-        <v>6527502</v>
+        <v>6527609</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805713</v>
+        <v>122805716</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505824</v>
+        <v>505804</v>
       </c>
       <c r="R81" t="n">
-        <v>6527597</v>
+        <v>6527537</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805709</v>
+        <v>122805717</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505799</v>
+        <v>505815</v>
       </c>
       <c r="R82" t="n">
-        <v>6527616</v>
+        <v>6527554</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,7 +9202,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805715</v>
+        <v>122805709</v>
       </c>
       <c r="B70" t="n">
         <v>83378</v>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505807</v>
+        <v>505799</v>
       </c>
       <c r="R70" t="n">
-        <v>6527517</v>
+        <v>6527616</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805707</v>
+        <v>122805706</v>
       </c>
       <c r="B71" t="n">
         <v>83378</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505815</v>
+        <v>505819</v>
       </c>
       <c r="R71" t="n">
-        <v>6527608</v>
+        <v>6527642</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805720</v>
+        <v>122805717</v>
       </c>
       <c r="B72" t="n">
         <v>83378</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505791</v>
+        <v>505815</v>
       </c>
       <c r="R72" t="n">
-        <v>6527512</v>
+        <v>6527554</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805708</v>
+        <v>122805713</v>
       </c>
       <c r="B73" t="n">
         <v>83378</v>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505802</v>
+        <v>505824</v>
       </c>
       <c r="R73" t="n">
-        <v>6527622</v>
+        <v>6527597</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805709</v>
+        <v>122805718</v>
       </c>
       <c r="B75" t="n">
         <v>83378</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505799</v>
+        <v>505822</v>
       </c>
       <c r="R75" t="n">
-        <v>6527616</v>
+        <v>6527537</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805706</v>
+        <v>122805715</v>
       </c>
       <c r="B76" t="n">
         <v>83378</v>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505819</v>
+        <v>505807</v>
       </c>
       <c r="R76" t="n">
-        <v>6527642</v>
+        <v>6527517</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805713</v>
+        <v>122805716</v>
       </c>
       <c r="B77" t="n">
         <v>83378</v>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505824</v>
+        <v>505804</v>
       </c>
       <c r="R77" t="n">
-        <v>6527597</v>
+        <v>6527537</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805718</v>
+        <v>122805707</v>
       </c>
       <c r="B78" t="n">
         <v>83378</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505822</v>
+        <v>505815</v>
       </c>
       <c r="R78" t="n">
-        <v>6527537</v>
+        <v>6527608</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,7 +10327,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805721</v>
+        <v>122805720</v>
       </c>
       <c r="B79" t="n">
         <v>83378</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505794</v>
+        <v>505791</v>
       </c>
       <c r="R79" t="n">
-        <v>6527502</v>
+        <v>6527512</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805716</v>
+        <v>122805721</v>
       </c>
       <c r="B81" t="n">
         <v>83378</v>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505804</v>
+        <v>505794</v>
       </c>
       <c r="R81" t="n">
-        <v>6527537</v>
+        <v>6527502</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805717</v>
+        <v>122805708</v>
       </c>
       <c r="B82" t="n">
         <v>83378</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505815</v>
+        <v>505802</v>
       </c>
       <c r="R82" t="n">
-        <v>6527554</v>
+        <v>6527622</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805709</v>
+        <v>122805706</v>
       </c>
       <c r="B70" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505799</v>
+        <v>505819</v>
       </c>
       <c r="R70" t="n">
-        <v>6527616</v>
+        <v>6527642</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805706</v>
+        <v>122805717</v>
       </c>
       <c r="B71" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505819</v>
+        <v>505815</v>
       </c>
       <c r="R71" t="n">
-        <v>6527642</v>
+        <v>6527554</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805717</v>
+        <v>122805707</v>
       </c>
       <c r="B72" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9504,7 +9504,7 @@
         <v>505815</v>
       </c>
       <c r="R72" t="n">
-        <v>6527554</v>
+        <v>6527608</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9580,7 +9580,7 @@
         <v>122805713</v>
       </c>
       <c r="B73" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805719</v>
+        <v>122805715</v>
       </c>
       <c r="B74" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505805</v>
+        <v>505807</v>
       </c>
       <c r="R74" t="n">
-        <v>6527537</v>
+        <v>6527517</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,10 +9827,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805718</v>
+        <v>122805716</v>
       </c>
       <c r="B75" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505822</v>
+        <v>505804</v>
       </c>
       <c r="R75" t="n">
         <v>6527537</v>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805715</v>
+        <v>122805709</v>
       </c>
       <c r="B76" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505807</v>
+        <v>505799</v>
       </c>
       <c r="R76" t="n">
-        <v>6527517</v>
+        <v>6527616</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,10 +10077,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805716</v>
+        <v>122805711</v>
       </c>
       <c r="B77" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505804</v>
+        <v>505805</v>
       </c>
       <c r="R77" t="n">
-        <v>6527537</v>
+        <v>6527609</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,10 +10202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805707</v>
+        <v>122805721</v>
       </c>
       <c r="B78" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505815</v>
+        <v>505794</v>
       </c>
       <c r="R78" t="n">
-        <v>6527608</v>
+        <v>6527502</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805720</v>
+        <v>122805708</v>
       </c>
       <c r="B79" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505791</v>
+        <v>505802</v>
       </c>
       <c r="R79" t="n">
-        <v>6527512</v>
+        <v>6527622</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805711</v>
+        <v>122805718</v>
       </c>
       <c r="B80" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505805</v>
+        <v>505822</v>
       </c>
       <c r="R80" t="n">
-        <v>6527609</v>
+        <v>6527537</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805721</v>
+        <v>122805720</v>
       </c>
       <c r="B81" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505794</v>
+        <v>505791</v>
       </c>
       <c r="R81" t="n">
-        <v>6527502</v>
+        <v>6527512</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805708</v>
+        <v>122805719</v>
       </c>
       <c r="B82" t="n">
-        <v>83378</v>
+        <v>83381</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505802</v>
+        <v>505805</v>
       </c>
       <c r="R82" t="n">
-        <v>6527622</v>
+        <v>6527537</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805706</v>
+        <v>122805718</v>
       </c>
       <c r="B70" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505819</v>
+        <v>505822</v>
       </c>
       <c r="R70" t="n">
-        <v>6527642</v>
+        <v>6527537</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805717</v>
+        <v>122805707</v>
       </c>
       <c r="B71" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9379,7 +9379,7 @@
         <v>505815</v>
       </c>
       <c r="R71" t="n">
-        <v>6527554</v>
+        <v>6527608</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805707</v>
+        <v>122805717</v>
       </c>
       <c r="B72" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9504,7 +9504,7 @@
         <v>505815</v>
       </c>
       <c r="R72" t="n">
-        <v>6527608</v>
+        <v>6527554</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805713</v>
+        <v>122805720</v>
       </c>
       <c r="B73" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505824</v>
+        <v>505791</v>
       </c>
       <c r="R73" t="n">
-        <v>6527597</v>
+        <v>6527512</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805715</v>
+        <v>122805708</v>
       </c>
       <c r="B74" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505807</v>
+        <v>505802</v>
       </c>
       <c r="R74" t="n">
-        <v>6527517</v>
+        <v>6527622</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9830,7 +9830,7 @@
         <v>122805716</v>
       </c>
       <c r="B75" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805709</v>
+        <v>122805711</v>
       </c>
       <c r="B76" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505799</v>
+        <v>505805</v>
       </c>
       <c r="R76" t="n">
-        <v>6527616</v>
+        <v>6527609</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,10 +10077,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805711</v>
+        <v>122805719</v>
       </c>
       <c r="B77" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10129,7 +10129,7 @@
         <v>505805</v>
       </c>
       <c r="R77" t="n">
-        <v>6527609</v>
+        <v>6527537</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,10 +10202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805721</v>
+        <v>122805706</v>
       </c>
       <c r="B78" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505794</v>
+        <v>505819</v>
       </c>
       <c r="R78" t="n">
-        <v>6527502</v>
+        <v>6527642</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805708</v>
+        <v>122805713</v>
       </c>
       <c r="B79" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505802</v>
+        <v>505824</v>
       </c>
       <c r="R79" t="n">
-        <v>6527622</v>
+        <v>6527597</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805718</v>
+        <v>122805709</v>
       </c>
       <c r="B80" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505822</v>
+        <v>505799</v>
       </c>
       <c r="R80" t="n">
-        <v>6527537</v>
+        <v>6527616</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805720</v>
+        <v>122805721</v>
       </c>
       <c r="B81" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505791</v>
+        <v>505794</v>
       </c>
       <c r="R81" t="n">
-        <v>6527512</v>
+        <v>6527502</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805719</v>
+        <v>122805715</v>
       </c>
       <c r="B82" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505805</v>
+        <v>505807</v>
       </c>
       <c r="R82" t="n">
-        <v>6527537</v>
+        <v>6527517</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805718</v>
+        <v>122805713</v>
       </c>
       <c r="B70" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505822</v>
+        <v>505824</v>
       </c>
       <c r="R70" t="n">
-        <v>6527537</v>
+        <v>6527597</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805707</v>
+        <v>122805715</v>
       </c>
       <c r="B71" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505815</v>
+        <v>505807</v>
       </c>
       <c r="R71" t="n">
-        <v>6527608</v>
+        <v>6527517</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805717</v>
+        <v>122805719</v>
       </c>
       <c r="B72" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505815</v>
+        <v>505805</v>
       </c>
       <c r="R72" t="n">
-        <v>6527554</v>
+        <v>6527537</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805720</v>
+        <v>122805711</v>
       </c>
       <c r="B73" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505791</v>
+        <v>505805</v>
       </c>
       <c r="R73" t="n">
-        <v>6527512</v>
+        <v>6527609</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805708</v>
+        <v>122805718</v>
       </c>
       <c r="B74" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505802</v>
+        <v>505822</v>
       </c>
       <c r="R74" t="n">
-        <v>6527622</v>
+        <v>6527537</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,10 +9827,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805716</v>
+        <v>122805706</v>
       </c>
       <c r="B75" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505804</v>
+        <v>505819</v>
       </c>
       <c r="R75" t="n">
-        <v>6527537</v>
+        <v>6527642</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805711</v>
+        <v>122805708</v>
       </c>
       <c r="B76" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505805</v>
+        <v>505802</v>
       </c>
       <c r="R76" t="n">
-        <v>6527609</v>
+        <v>6527622</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,10 +10077,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805719</v>
+        <v>122805707</v>
       </c>
       <c r="B77" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505805</v>
+        <v>505815</v>
       </c>
       <c r="R77" t="n">
-        <v>6527537</v>
+        <v>6527608</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,10 +10202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805706</v>
+        <v>122805720</v>
       </c>
       <c r="B78" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505819</v>
+        <v>505791</v>
       </c>
       <c r="R78" t="n">
-        <v>6527642</v>
+        <v>6527512</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805713</v>
+        <v>122805709</v>
       </c>
       <c r="B79" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505824</v>
+        <v>505799</v>
       </c>
       <c r="R79" t="n">
-        <v>6527597</v>
+        <v>6527616</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805709</v>
+        <v>122805716</v>
       </c>
       <c r="B80" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505799</v>
+        <v>505804</v>
       </c>
       <c r="R80" t="n">
-        <v>6527616</v>
+        <v>6527537</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805721</v>
+        <v>122805717</v>
       </c>
       <c r="B81" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505794</v>
+        <v>505815</v>
       </c>
       <c r="R81" t="n">
-        <v>6527502</v>
+        <v>6527554</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805715</v>
+        <v>122805721</v>
       </c>
       <c r="B82" t="n">
-        <v>83383</v>
+        <v>83385</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505807</v>
+        <v>505794</v>
       </c>
       <c r="R82" t="n">
-        <v>6527517</v>
+        <v>6527502</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -9202,10 +9202,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805713</v>
+        <v>122805706</v>
       </c>
       <c r="B70" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505824</v>
+        <v>505819</v>
       </c>
       <c r="R70" t="n">
-        <v>6527597</v>
+        <v>6527642</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805715</v>
+        <v>122805716</v>
       </c>
       <c r="B71" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505807</v>
+        <v>505804</v>
       </c>
       <c r="R71" t="n">
-        <v>6527517</v>
+        <v>6527537</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805719</v>
+        <v>122805708</v>
       </c>
       <c r="B72" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505805</v>
+        <v>505802</v>
       </c>
       <c r="R72" t="n">
-        <v>6527537</v>
+        <v>6527622</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805711</v>
+        <v>122805713</v>
       </c>
       <c r="B73" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505805</v>
+        <v>505824</v>
       </c>
       <c r="R73" t="n">
-        <v>6527609</v>
+        <v>6527597</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805718</v>
+        <v>122805715</v>
       </c>
       <c r="B74" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505822</v>
+        <v>505807</v>
       </c>
       <c r="R74" t="n">
-        <v>6527537</v>
+        <v>6527517</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,10 +9827,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805706</v>
+        <v>122805718</v>
       </c>
       <c r="B75" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505819</v>
+        <v>505822</v>
       </c>
       <c r="R75" t="n">
-        <v>6527642</v>
+        <v>6527537</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805708</v>
+        <v>122805709</v>
       </c>
       <c r="B76" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505802</v>
+        <v>505799</v>
       </c>
       <c r="R76" t="n">
-        <v>6527622</v>
+        <v>6527616</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,10 +10077,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805707</v>
+        <v>122805711</v>
       </c>
       <c r="B77" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505815</v>
+        <v>505805</v>
       </c>
       <c r="R77" t="n">
-        <v>6527608</v>
+        <v>6527609</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10205,7 +10205,7 @@
         <v>122805720</v>
       </c>
       <c r="B78" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805709</v>
+        <v>122805707</v>
       </c>
       <c r="B79" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>505799</v>
+        <v>505815</v>
       </c>
       <c r="R79" t="n">
-        <v>6527616</v>
+        <v>6527608</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122805716</v>
+        <v>122805721</v>
       </c>
       <c r="B80" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505804</v>
+        <v>505794</v>
       </c>
       <c r="R80" t="n">
-        <v>6527537</v>
+        <v>6527502</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122805717</v>
+        <v>122805719</v>
       </c>
       <c r="B81" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505815</v>
+        <v>505805</v>
       </c>
       <c r="R81" t="n">
-        <v>6527554</v>
+        <v>6527537</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122805721</v>
+        <v>122805717</v>
       </c>
       <c r="B82" t="n">
-        <v>83385</v>
+        <v>83388</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505794</v>
+        <v>505815</v>
       </c>
       <c r="R82" t="n">
-        <v>6527502</v>
+        <v>6527554</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7395,7 +7395,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116158230</v>
+        <v>116158232</v>
       </c>
       <c r="B53" t="n">
         <v>83124</v>
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>505805</v>
+        <v>505800</v>
       </c>
       <c r="R53" t="n">
-        <v>6527509</v>
+        <v>6527648</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116158232</v>
+        <v>116158229</v>
       </c>
       <c r="B54" t="n">
         <v>83124</v>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>505800</v>
+        <v>505793</v>
       </c>
       <c r="R54" t="n">
-        <v>6527648</v>
+        <v>6527503</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7609,10 +7609,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116158229</v>
+        <v>116158235</v>
       </c>
       <c r="B55" t="n">
-        <v>83124</v>
+        <v>94230</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7621,42 +7621,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1633</v>
+        <v>2671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rökpipsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Urnula craterium</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>505793</v>
+        <v>505803</v>
       </c>
       <c r="R55" t="n">
-        <v>6527503</v>
+        <v>6527576</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7697,7 +7693,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7716,10 +7711,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116158235</v>
+        <v>116161229</v>
       </c>
       <c r="B56" t="n">
-        <v>94230</v>
+        <v>99992</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7732,34 +7727,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Önnabo, Nrk</t>
+          <t>Lillsjökärret, Nrk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>505803</v>
+        <v>505814</v>
       </c>
       <c r="R56" t="n">
-        <v>6527576</v>
+        <v>6527593</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7811,17 +7806,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Rolf Wedding</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116161229</v>
+        <v>116158226</v>
       </c>
       <c r="B57" t="n">
-        <v>99992</v>
+        <v>94245</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7834,34 +7829,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillsjökärret, Nrk</t>
+          <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>505814</v>
+        <v>505797</v>
       </c>
       <c r="R57" t="n">
-        <v>6527593</v>
+        <v>6527573</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7913,17 +7908,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Rolf Wedding</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116158226</v>
+        <v>116158228</v>
       </c>
       <c r="B58" t="n">
-        <v>94245</v>
+        <v>83124</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7932,38 +7927,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2668</v>
+        <v>1633</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Rökpipsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Urnula craterium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>505797</v>
+        <v>505825</v>
       </c>
       <c r="R58" t="n">
-        <v>6527573</v>
+        <v>6527579</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8004,6 +8003,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>116036546</v>
+        <v>116037802</v>
       </c>
       <c r="B59" t="n">
         <v>83124</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>505805</v>
+        <v>505799</v>
       </c>
       <c r="R59" t="n">
-        <v>6527510</v>
+        <v>6527610</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8136,7 +8136,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116158228</v>
+        <v>116038032</v>
       </c>
       <c r="B60" t="n">
         <v>83124</v>
@@ -8171,22 +8171,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Önnabo, Nrk</t>
+          <t>Önnabo (Önnabo), Nrk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>505825</v>
+        <v>505834</v>
       </c>
       <c r="R60" t="n">
-        <v>6527579</v>
+        <v>6527645</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8210,12 +8217,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8231,22 +8238,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Rolf Wedding</t>
+          <t>Henrik Josefsson, Marie Winsa, Charlotte Uddén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>116037802</v>
+        <v>116158223</v>
       </c>
       <c r="B61" t="n">
-        <v>83124</v>
+        <v>106089</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8255,52 +8262,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1633</v>
+        <v>219686</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rökpipsvamp</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Urnula craterium</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Önnabo (Önnabo), Nrk</t>
+          <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>505799</v>
+        <v>505822</v>
       </c>
       <c r="R61" t="n">
-        <v>6527610</v>
+        <v>6527650</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8324,12 +8320,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8338,26 +8334,25 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Henrik Josefsson, Marie Winsa, Charlotte Uddén</t>
+          <t>Marika Sjödin, Rolf Wedding</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>116038032</v>
+        <v>116037988</v>
       </c>
       <c r="B62" t="n">
         <v>83124</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8408,10 +8403,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>505834</v>
+        <v>505812</v>
       </c>
       <c r="R62" t="n">
-        <v>6527645</v>
+        <v>6527663</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8471,7 +8466,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116158223</v>
+        <v>116158225</v>
       </c>
       <c r="B63" t="n">
         <v>106089</v>
@@ -8511,10 +8506,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>505822</v>
+        <v>505799</v>
       </c>
       <c r="R63" t="n">
-        <v>6527650</v>
+        <v>6527607</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8573,10 +8568,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116037988</v>
+        <v>116158234</v>
       </c>
       <c r="B64" t="n">
-        <v>83124</v>
+        <v>90968</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8585,52 +8580,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1633</v>
+        <v>3884</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rökpipsvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Urnula craterium</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Önnabo (Önnabo), Nrk</t>
+          <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>505812</v>
+        <v>505821</v>
       </c>
       <c r="R64" t="n">
-        <v>6527663</v>
+        <v>6527608</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8654,12 +8638,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8668,29 +8652,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Henrik Josefsson, Marie Winsa, Charlotte Uddén</t>
+          <t>Marika Sjödin, Rolf Wedding</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>116158225</v>
+        <v>116158231</v>
       </c>
       <c r="B65" t="n">
-        <v>106089</v>
+        <v>83124</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8699,38 +8682,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219686</v>
+        <v>1633</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Rökpipsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Urnula craterium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>505799</v>
+        <v>505803</v>
       </c>
       <c r="R65" t="n">
-        <v>6527607</v>
+        <v>6527609</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8771,6 +8758,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8789,10 +8777,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>116158234</v>
+        <v>116158221</v>
       </c>
       <c r="B66" t="n">
-        <v>90968</v>
+        <v>106089</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8805,21 +8793,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3884</v>
+        <v>219686</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8829,10 +8817,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>505821</v>
+        <v>505802</v>
       </c>
       <c r="R66" t="n">
-        <v>6527608</v>
+        <v>6527621</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8891,10 +8879,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>116158231</v>
+        <v>116161230</v>
       </c>
       <c r="B67" t="n">
-        <v>83124</v>
+        <v>99992</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8903,42 +8891,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1633</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rökpipsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Urnula craterium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Önnabo, Nrk</t>
+          <t>Lillsjökärret, Nrk</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>505803</v>
+        <v>505802</v>
       </c>
       <c r="R67" t="n">
-        <v>6527609</v>
+        <v>6527621</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8979,7 +8963,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8991,17 +8974,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Rolf Wedding</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>116158221</v>
+        <v>122805706</v>
       </c>
       <c r="B68" t="n">
-        <v>106089</v>
+        <v>83388</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9010,41 +8993,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219686</v>
+        <v>1633</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Rökpipsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Urnula craterium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>505802</v>
+        <v>505819</v>
       </c>
       <c r="R68" t="n">
-        <v>6527621</v>
+        <v>6527642</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9068,12 +9060,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9084,26 +9081,35 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Rolf Wedding</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>116161230</v>
+        <v>122805716</v>
       </c>
       <c r="B69" t="n">
-        <v>99992</v>
+        <v>83388</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9112,41 +9118,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>1633</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rökpipsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Urnula craterium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillsjökärret, Nrk</t>
+          <t>Önnabo, Nrk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>505802</v>
+        <v>505804</v>
       </c>
       <c r="R69" t="n">
-        <v>6527621</v>
+        <v>6527537</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9170,12 +9185,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9186,23 +9206,32 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Död ved på marken av hassel</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för rökpipsvamp</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122805706</v>
+        <v>122805708</v>
       </c>
       <c r="B70" t="n">
         <v>83388</v>
@@ -9237,7 +9266,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9251,10 +9280,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>505819</v>
+        <v>505802</v>
       </c>
       <c r="R70" t="n">
-        <v>6527642</v>
+        <v>6527622</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9327,7 +9356,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122805716</v>
+        <v>122805713</v>
       </c>
       <c r="B71" t="n">
         <v>83388</v>
@@ -9362,7 +9391,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9376,10 +9405,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>505804</v>
+        <v>505824</v>
       </c>
       <c r="R71" t="n">
-        <v>6527537</v>
+        <v>6527597</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9452,7 +9481,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122805708</v>
+        <v>122805715</v>
       </c>
       <c r="B72" t="n">
         <v>83388</v>
@@ -9487,7 +9516,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9501,10 +9530,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>505802</v>
+        <v>505807</v>
       </c>
       <c r="R72" t="n">
-        <v>6527622</v>
+        <v>6527517</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9577,7 +9606,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122805713</v>
+        <v>122805718</v>
       </c>
       <c r="B73" t="n">
         <v>83388</v>
@@ -9612,7 +9641,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9626,10 +9655,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>505824</v>
+        <v>505822</v>
       </c>
       <c r="R73" t="n">
-        <v>6527597</v>
+        <v>6527537</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9702,7 +9731,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122805715</v>
+        <v>122805711</v>
       </c>
       <c r="B74" t="n">
         <v>83388</v>
@@ -9737,7 +9766,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9751,10 +9780,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>505807</v>
+        <v>505805</v>
       </c>
       <c r="R74" t="n">
-        <v>6527517</v>
+        <v>6527609</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9827,7 +9856,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122805718</v>
+        <v>122805720</v>
       </c>
       <c r="B75" t="n">
         <v>83388</v>
@@ -9862,7 +9891,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9876,10 +9905,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>505822</v>
+        <v>505791</v>
       </c>
       <c r="R75" t="n">
-        <v>6527537</v>
+        <v>6527512</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9952,7 +9981,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122805711</v>
+        <v>122805707</v>
       </c>
       <c r="B76" t="n">
         <v>83388</v>
@@ -9987,7 +10016,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10001,10 +10030,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>505805</v>
+        <v>505815</v>
       </c>
       <c r="R76" t="n">
-        <v>6527609</v>
+        <v>6527608</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10077,7 +10106,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122805709</v>
+        <v>122805721</v>
       </c>
       <c r="B77" t="n">
         <v>83388</v>
@@ -10112,7 +10141,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10126,10 +10155,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>505799</v>
+        <v>505794</v>
       </c>
       <c r="R77" t="n">
-        <v>6527616</v>
+        <v>6527502</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10202,7 +10231,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122805720</v>
+        <v>122805719</v>
       </c>
       <c r="B78" t="n">
         <v>83388</v>
@@ -10251,10 +10280,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>505791</v>
+        <v>505805</v>
       </c>
       <c r="R78" t="n">
-        <v>6527512</v>
+        <v>6527537</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10327,7 +10356,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122805707</v>
+        <v>122805717</v>
       </c>
       <c r="B79" t="n">
         <v>83388</v>
@@ -10362,7 +10391,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10379,7 +10408,7 @@
         <v>505815</v>
       </c>
       <c r="R79" t="n">
-        <v>6527608</v>
+        <v>6527554</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10445,381 +10474,6 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för rökpipsvamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>122805721</v>
-      </c>
-      <c r="B80" t="n">
-        <v>83388</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1633</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Rökpipsvamp</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Urnula craterium</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Önnabo, Nrk</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>505794</v>
-      </c>
-      <c r="R80" t="n">
-        <v>6527502</v>
-      </c>
-      <c r="S80" t="n">
-        <v>5</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Död ved på marken av hassel</t>
-        </is>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson, Marie Winsa</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för rökpipsvamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>122805719</v>
-      </c>
-      <c r="B81" t="n">
-        <v>83388</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>1633</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Rökpipsvamp</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Urnula craterium</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Önnabo, Nrk</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>505805</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6527537</v>
-      </c>
-      <c r="S81" t="n">
-        <v>5</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Död ved på marken av hassel</t>
-        </is>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson, Marie Winsa</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för rökpipsvamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>122805717</v>
-      </c>
-      <c r="B82" t="n">
-        <v>83388</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>1633</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Rökpipsvamp</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Urnula craterium</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Önnabo, Nrk</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>505815</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6527554</v>
-      </c>
-      <c r="S82" t="n">
-        <v>5</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Uppföljning av åtgärd som genomförts tidigare i vinter.</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Död ved på marken av hassel</t>
-        </is>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson, Marie Winsa</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10479,6 +10479,2086 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131893407</v>
+      </c>
+      <c r="B80" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>505819</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6527653</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131893394</v>
+      </c>
+      <c r="B81" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>505798</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6527570</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131893395</v>
+      </c>
+      <c r="B82" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>505789</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6527527</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131893390</v>
+      </c>
+      <c r="B83" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>505805</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6527624</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131893400</v>
+      </c>
+      <c r="B84" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>505805</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6527526</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131893399</v>
+      </c>
+      <c r="B85" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>505801</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6527500</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131893403</v>
+      </c>
+      <c r="B86" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>505819</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6527592</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131893406</v>
+      </c>
+      <c r="B87" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>505833</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6527647</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>131893391</v>
+      </c>
+      <c r="B88" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>505806</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6527620</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131893405</v>
+      </c>
+      <c r="B89" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>505815</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6527610</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131893396</v>
+      </c>
+      <c r="B90" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>505785</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6527525</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>131893404</v>
+      </c>
+      <c r="B91" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>505816</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6527611</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>131893401</v>
+      </c>
+      <c r="B92" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>505811</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6527535</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>131893402</v>
+      </c>
+      <c r="B93" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>505802</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6527540</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>131893393</v>
+      </c>
+      <c r="B94" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>505804</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6527568</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>131893392</v>
+      </c>
+      <c r="B95" t="n">
+        <v>84098</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Önnabo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>505802</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6527616</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Corylus avellana # Död ved av hassel</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Marie Winsa</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10481,10 +10481,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131893407</v>
+        <v>131893394</v>
       </c>
       <c r="B80" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505819</v>
+        <v>505798</v>
       </c>
       <c r="R80" t="n">
-        <v>6527653</v>
+        <v>6527570</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10611,10 +10611,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131893394</v>
+        <v>131893407</v>
       </c>
       <c r="B81" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10655,10 +10655,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505798</v>
+        <v>505819</v>
       </c>
       <c r="R81" t="n">
-        <v>6527570</v>
+        <v>6527653</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131893395</v>
+        <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10785,10 +10785,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>505789</v>
+        <v>505805</v>
       </c>
       <c r="R82" t="n">
-        <v>6527527</v>
+        <v>6527624</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10871,10 +10871,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131893390</v>
+        <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>505805</v>
+        <v>505789</v>
       </c>
       <c r="R83" t="n">
-        <v>6527624</v>
+        <v>6527527</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131893403</v>
+        <v>131893406</v>
       </c>
       <c r="B86" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11305,10 +11305,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>505819</v>
+        <v>505833</v>
       </c>
       <c r="R86" t="n">
-        <v>6527592</v>
+        <v>6527647</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11391,10 +11391,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131893406</v>
+        <v>131893403</v>
       </c>
       <c r="B87" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>505833</v>
+        <v>505819</v>
       </c>
       <c r="R87" t="n">
-        <v>6527647</v>
+        <v>6527592</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11521,10 +11521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131893391</v>
+        <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>505806</v>
+        <v>505815</v>
       </c>
       <c r="R88" t="n">
-        <v>6527620</v>
+        <v>6527610</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -11651,10 +11651,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131893405</v>
+        <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>505815</v>
+        <v>505785</v>
       </c>
       <c r="R89" t="n">
-        <v>6527610</v>
+        <v>6527525</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11781,10 +11781,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131893396</v>
+        <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>505785</v>
+        <v>505806</v>
       </c>
       <c r="R90" t="n">
-        <v>6527525</v>
+        <v>6527620</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84098</v>
+        <v>84099</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10484,7 +10484,7 @@
         <v>131893394</v>
       </c>
       <c r="B80" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>131893407</v>
       </c>
       <c r="B81" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>131893406</v>
       </c>
       <c r="B86" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>131893403</v>
       </c>
       <c r="B87" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84099</v>
+        <v>84102</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10481,10 +10481,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131893394</v>
+        <v>131893407</v>
       </c>
       <c r="B80" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505798</v>
+        <v>505819</v>
       </c>
       <c r="R80" t="n">
-        <v>6527570</v>
+        <v>6527653</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10611,10 +10611,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131893407</v>
+        <v>131893394</v>
       </c>
       <c r="B81" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10655,10 +10655,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505819</v>
+        <v>505798</v>
       </c>
       <c r="R81" t="n">
-        <v>6527653</v>
+        <v>6527570</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10744,7 +10744,7 @@
         <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131893406</v>
+        <v>131893403</v>
       </c>
       <c r="B86" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11305,10 +11305,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>505833</v>
+        <v>505819</v>
       </c>
       <c r="R86" t="n">
-        <v>6527647</v>
+        <v>6527592</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11391,10 +11391,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131893403</v>
+        <v>131893406</v>
       </c>
       <c r="B87" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>505819</v>
+        <v>505833</v>
       </c>
       <c r="R87" t="n">
-        <v>6527592</v>
+        <v>6527647</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11524,7 +11524,7 @@
         <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84102</v>
+        <v>84107</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10481,10 +10481,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131893407</v>
+        <v>131893394</v>
       </c>
       <c r="B80" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>505819</v>
+        <v>505798</v>
       </c>
       <c r="R80" t="n">
-        <v>6527653</v>
+        <v>6527570</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10611,10 +10611,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131893394</v>
+        <v>131893407</v>
       </c>
       <c r="B81" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10655,10 +10655,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>505798</v>
+        <v>505819</v>
       </c>
       <c r="R81" t="n">
-        <v>6527570</v>
+        <v>6527653</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10744,7 +10744,7 @@
         <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131893403</v>
+        <v>131893406</v>
       </c>
       <c r="B86" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11305,10 +11305,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>505819</v>
+        <v>505833</v>
       </c>
       <c r="R86" t="n">
-        <v>6527592</v>
+        <v>6527647</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11391,10 +11391,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131893406</v>
+        <v>131893403</v>
       </c>
       <c r="B87" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>505833</v>
+        <v>505819</v>
       </c>
       <c r="R87" t="n">
-        <v>6527647</v>
+        <v>6527592</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11524,7 +11524,7 @@
         <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84107</v>
+        <v>84109</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -11651,7 +11651,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131893396</v>
+        <v>131893391</v>
       </c>
       <c r="B89" t="n">
         <v>84109</v>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>505785</v>
+        <v>505806</v>
       </c>
       <c r="R89" t="n">
-        <v>6527525</v>
+        <v>6527620</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11781,7 +11781,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131893391</v>
+        <v>131893396</v>
       </c>
       <c r="B90" t="n">
         <v>84109</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>505806</v>
+        <v>505785</v>
       </c>
       <c r="R90" t="n">
-        <v>6527620</v>
+        <v>6527525</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -11651,7 +11651,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131893391</v>
+        <v>131893396</v>
       </c>
       <c r="B89" t="n">
         <v>84109</v>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>505806</v>
+        <v>505785</v>
       </c>
       <c r="R89" t="n">
-        <v>6527620</v>
+        <v>6527525</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11781,7 +11781,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131893396</v>
+        <v>131893391</v>
       </c>
       <c r="B90" t="n">
         <v>84109</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>505785</v>
+        <v>505806</v>
       </c>
       <c r="R90" t="n">
-        <v>6527525</v>
+        <v>6527620</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10484,7 +10484,7 @@
         <v>131893394</v>
       </c>
       <c r="B80" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>131893407</v>
       </c>
       <c r="B81" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>131893406</v>
       </c>
       <c r="B86" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>131893403</v>
       </c>
       <c r="B87" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84109</v>
+        <v>84143</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10484,7 +10484,7 @@
         <v>131893394</v>
       </c>
       <c r="B80" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>131893407</v>
       </c>
       <c r="B81" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>131893406</v>
       </c>
       <c r="B86" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>131893403</v>
       </c>
       <c r="B87" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -10484,7 +10484,7 @@
         <v>131893394</v>
       </c>
       <c r="B80" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>131893407</v>
       </c>
       <c r="B81" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>131893390</v>
       </c>
       <c r="B82" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131893395</v>
       </c>
       <c r="B83" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>131893400</v>
       </c>
       <c r="B84" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>131893399</v>
       </c>
       <c r="B85" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>131893406</v>
       </c>
       <c r="B86" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>131893403</v>
       </c>
       <c r="B87" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>131893405</v>
       </c>
       <c r="B88" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>131893396</v>
       </c>
       <c r="B89" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>131893391</v>
       </c>
       <c r="B90" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>131893404</v>
       </c>
       <c r="B91" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>131893401</v>
       </c>
       <c r="B92" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>131893402</v>
       </c>
       <c r="B93" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>131893393</v>
       </c>
       <c r="B94" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>131893392</v>
       </c>
       <c r="B95" t="n">
-        <v>84150</v>
+        <v>84152</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12559,6 +12559,112 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133531732</v>
+      </c>
+      <c r="B96" t="n">
+        <v>84168</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1633</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Rökpipsvamp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Urnula craterium</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Greveslätten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>505784</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6527555</v>
+      </c>
+      <c r="S96" t="n">
+        <v>50</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ett förtorkat exemplar</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -12564,7 +12564,7 @@
         <v>133531732</v>
       </c>
       <c r="B96" t="n">
-        <v>84168</v>
+        <v>84169</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -12564,7 +12564,7 @@
         <v>133531732</v>
       </c>
       <c r="B96" t="n">
-        <v>84169</v>
+        <v>84172</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -12564,7 +12564,7 @@
         <v>133531732</v>
       </c>
       <c r="B96" t="n">
-        <v>84172</v>
+        <v>84186</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -12564,7 +12564,7 @@
         <v>133531732</v>
       </c>
       <c r="B96" t="n">
-        <v>84186</v>
+        <v>84196</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -12564,7 +12564,7 @@
         <v>133531732</v>
       </c>
       <c r="B96" t="n">
-        <v>84196</v>
+        <v>84197</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 58660-2024 artfynd.xlsx
+++ b/artfynd/A 58660-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AZ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476423</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476424</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476426</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476427</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476428</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476429</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476430</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1797,6 +1842,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476431</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1922,6 +1972,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476432</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2047,6 +2102,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476433</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2172,6 +2232,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476434</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2297,6 +2362,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476435</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2425,6 +2495,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932558</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2553,6 +2628,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932559</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2681,6 +2761,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932560</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2809,6 +2894,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932561</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2937,6 +3027,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932562</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3065,6 +3160,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932563</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3193,6 +3293,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932564</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3321,6 +3426,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932565</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3449,6 +3559,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932566</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3577,6 +3692,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932567</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3705,6 +3825,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932568</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3833,6 +3958,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932569</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3961,6 +4091,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932570</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4078,6 +4213,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108586581</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4215,6 +4355,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587023</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4347,6 +4492,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587705</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4479,6 +4629,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587935</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4596,6 +4751,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588156</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4713,6 +4873,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588657</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4830,6 +4995,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705192</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4949,6 +5119,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705584</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5058,6 +5233,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705723</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5175,6 +5355,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705841</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5284,6 +5469,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116035595</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5393,6 +5583,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116036546</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5502,6 +5697,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116037802</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5611,6 +5811,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116037843</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5720,6 +5925,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116037988</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5829,6 +6039,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116038032</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5931,6 +6146,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158228</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6033,6 +6253,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158229</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6135,6 +6360,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158230</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6237,6 +6467,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158231</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6339,6 +6574,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158232</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6459,6 +6699,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805706</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6579,6 +6824,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805707</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6699,6 +6949,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805708</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6819,6 +7074,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805709</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6939,6 +7199,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805711</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7059,6 +7324,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805713</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7179,6 +7449,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805715</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7299,6 +7574,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805716</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7419,6 +7699,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805717</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7539,6 +7824,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805718</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7659,6 +7949,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805719</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7779,6 +8074,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805720</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7899,6 +8199,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805721</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8029,6 +8334,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893390</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8159,6 +8469,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893391</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8289,6 +8604,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893392</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8419,6 +8739,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893393</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8549,6 +8874,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893394</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8679,6 +9009,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893395</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8809,6 +9144,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893396</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8939,6 +9279,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893398</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9069,6 +9414,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893399</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9199,6 +9549,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893400</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9329,6 +9684,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893401</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9459,6 +9819,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893402</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9589,6 +9954,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893403</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9719,6 +10089,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893404</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9849,6 +10224,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893405</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9979,6 +10359,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893406</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10107,6 +10492,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893407</t>
         </is>
       </c>
     </row>
@@ -10215,6 +10605,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133531732</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10312,6 +10707,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158226</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10409,6 +10809,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158235</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10525,6 +10930,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1170590</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10622,6 +11032,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158234</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10724,6 +11139,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2204521</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10845,6 +11265,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587921</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10962,6 +11387,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588735</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11059,6 +11489,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158221</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11156,6 +11591,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158222</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11253,6 +11693,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158223</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11350,6 +11795,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158224</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11447,6 +11897,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158225</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11553,6 +12008,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62421602</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11655,6 +12115,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2632921</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11757,6 +12222,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62124149</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11859,6 +12329,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62531177</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11966,6 +12441,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62531179</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12068,6 +12548,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5019490</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12170,6 +12655,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082620</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12267,6 +12757,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161229</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12364,6 +12859,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161230</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12461,6 +12961,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161231</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12563,6 +13068,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59855075</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12665,8 +13175,117 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59855076</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>